--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:00</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:19</t>
+    <t xml:space="preserve">2026-10-04 08:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:47</t>
+    <t xml:space="preserve">2026-10-05 09:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>841466.62</v>
+        <v>841466.63</v>
       </c>
     </row>
     <row r="3">
@@ -610,7 +610,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>696530.12</v>
+        <v>696530.13</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>666224.12</v>
+        <v>666224.13</v>
       </c>
     </row>
     <row r="10">
